--- a/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -713,13 +713,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>12205500</v>
+        <v>12172100</v>
       </c>
       <c r="E8" s="3">
-        <v>8744200</v>
+        <v>8720300</v>
       </c>
       <c r="F8" s="3">
-        <v>8746800</v>
+        <v>8722900</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -743,13 +743,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9455800</v>
+        <v>9430000</v>
       </c>
       <c r="E9" s="3">
-        <v>6405300</v>
+        <v>6387800</v>
       </c>
       <c r="F9" s="3">
-        <v>6291800</v>
+        <v>6274600</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -773,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2749600</v>
+        <v>2742100</v>
       </c>
       <c r="E10" s="3">
-        <v>2338900</v>
+        <v>2332500</v>
       </c>
       <c r="F10" s="3">
-        <v>2455000</v>
+        <v>2448300</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -880,10 +880,10 @@
         <v>19600</v>
       </c>
       <c r="E14" s="3">
-        <v>36400</v>
+        <v>36300</v>
       </c>
       <c r="F14" s="3">
-        <v>127900</v>
+        <v>126500</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10781100</v>
+        <v>10751700</v>
       </c>
       <c r="E17" s="3">
-        <v>7701600</v>
+        <v>7680600</v>
       </c>
       <c r="F17" s="3">
-        <v>7663500</v>
+        <v>7642600</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -978,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1424300</v>
+        <v>1420500</v>
       </c>
       <c r="E18" s="3">
-        <v>1042600</v>
+        <v>1039700</v>
       </c>
       <c r="F18" s="3">
-        <v>1083300</v>
+        <v>1080300</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1022,13 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>560900</v>
+        <v>559300</v>
       </c>
       <c r="E20" s="3">
-        <v>473100</v>
+        <v>471800</v>
       </c>
       <c r="F20" s="3">
-        <v>638000</v>
+        <v>636200</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1052,10 +1052,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2400900</v>
+        <v>2394600</v>
       </c>
       <c r="E21" s="3">
-        <v>1946900</v>
+        <v>1941800</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1082,13 +1082,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>691000</v>
+        <v>689100</v>
       </c>
       <c r="E22" s="3">
-        <v>334500</v>
+        <v>333600</v>
       </c>
       <c r="F22" s="3">
-        <v>396700</v>
+        <v>395600</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1112,13 +1112,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1294200</v>
+        <v>1290700</v>
       </c>
       <c r="E23" s="3">
-        <v>1181200</v>
+        <v>1178000</v>
       </c>
       <c r="F23" s="3">
-        <v>1324500</v>
+        <v>1320900</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1142,13 +1142,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>771100</v>
+        <v>769000</v>
       </c>
       <c r="E24" s="3">
-        <v>629800</v>
+        <v>628000</v>
       </c>
       <c r="F24" s="3">
-        <v>725800</v>
+        <v>723800</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1202,13 +1202,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>523100</v>
+        <v>521700</v>
       </c>
       <c r="E26" s="3">
-        <v>551400</v>
+        <v>549900</v>
       </c>
       <c r="F26" s="3">
-        <v>598800</v>
+        <v>597100</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1232,13 +1232,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>125200</v>
+        <v>124800</v>
       </c>
       <c r="E27" s="3">
-        <v>160100</v>
+        <v>159700</v>
       </c>
       <c r="F27" s="3">
-        <v>147600</v>
+        <v>147200</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1382,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-560900</v>
+        <v>-559300</v>
       </c>
       <c r="E32" s="3">
-        <v>-473100</v>
+        <v>-471800</v>
       </c>
       <c r="F32" s="3">
-        <v>-638000</v>
+        <v>-636200</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1412,13 +1412,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>125200</v>
+        <v>124800</v>
       </c>
       <c r="E33" s="3">
-        <v>160100</v>
+        <v>159700</v>
       </c>
       <c r="F33" s="3">
-        <v>147600</v>
+        <v>147200</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1472,13 +1472,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>125200</v>
+        <v>124800</v>
       </c>
       <c r="E35" s="3">
-        <v>160100</v>
+        <v>159700</v>
       </c>
       <c r="F35" s="3">
-        <v>147600</v>
+        <v>147200</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1565,10 +1565,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6827900</v>
+        <v>6809300</v>
       </c>
       <c r="E41" s="3">
-        <v>7398600</v>
+        <v>7378400</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1595,10 +1595,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1985400</v>
+        <v>1979900</v>
       </c>
       <c r="E42" s="3">
-        <v>1837400</v>
+        <v>1832400</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1625,10 +1625,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1601900</v>
+        <v>4571900</v>
       </c>
       <c r="E43" s="3">
-        <v>2539900</v>
+        <v>2533000</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1655,10 +1655,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10057600</v>
+        <v>10093700</v>
       </c>
       <c r="E44" s="3">
-        <v>10811800</v>
+        <v>10782200</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1685,10 +1685,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1627000</v>
+        <v>1622500</v>
       </c>
       <c r="E45" s="3">
-        <v>2174600</v>
+        <v>2168600</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1715,10 +1715,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22099700</v>
+        <v>21975400</v>
       </c>
       <c r="E46" s="3">
-        <v>24762200</v>
+        <v>24694600</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1745,10 +1745,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18790600</v>
+        <v>18905400</v>
       </c>
       <c r="E47" s="3">
-        <v>17531600</v>
+        <v>17483700</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1775,10 +1775,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31571200</v>
+        <v>34130000</v>
       </c>
       <c r="E48" s="3">
-        <v>33395300</v>
+        <v>33304100</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1805,10 +1805,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2770400</v>
+        <v>5525700</v>
       </c>
       <c r="E49" s="3">
-        <v>2744100</v>
+        <v>2736600</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1895,10 +1895,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3795100</v>
+        <v>7398500</v>
       </c>
       <c r="E52" s="3">
-        <v>3080800</v>
+        <v>3072400</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1955,10 +1955,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>79027000</v>
+        <v>77856300</v>
       </c>
       <c r="E54" s="3">
-        <v>81514000</v>
+        <v>81291400</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2013,10 +2013,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4318400</v>
+        <v>11639200</v>
       </c>
       <c r="E57" s="3">
-        <v>4419500</v>
+        <v>4407500</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2043,10 +2043,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6837600</v>
+        <v>6818900</v>
       </c>
       <c r="E58" s="3">
-        <v>6608800</v>
+        <v>6590800</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2073,10 +2073,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11823000</v>
+        <v>17697300</v>
       </c>
       <c r="E59" s="3">
-        <v>11124500</v>
+        <v>11094200</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2103,10 +2103,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22978900</v>
+        <v>22625700</v>
       </c>
       <c r="E60" s="3">
-        <v>22152900</v>
+        <v>22092400</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2133,10 +2133,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18233300</v>
+        <v>18183500</v>
       </c>
       <c r="E61" s="3">
-        <v>18915200</v>
+        <v>18863600</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2163,10 +2163,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3396800</v>
+        <v>4058800</v>
       </c>
       <c r="E62" s="3">
-        <v>3514500</v>
+        <v>3504900</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2283,10 +2283,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>47813800</v>
+        <v>46292500</v>
       </c>
       <c r="E66" s="3">
-        <v>48059700</v>
+        <v>47928400</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2447,10 +2447,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15084200</v>
+        <v>30521800</v>
       </c>
       <c r="E72" s="3">
-        <v>17302800</v>
+        <v>17255600</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2567,10 +2567,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31213200</v>
+        <v>31563900</v>
       </c>
       <c r="E76" s="3">
-        <v>33454300</v>
+        <v>33363000</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2662,13 +2662,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>125200</v>
+        <v>124800</v>
       </c>
       <c r="E81" s="3">
-        <v>160100</v>
+        <v>159700</v>
       </c>
       <c r="F81" s="3">
-        <v>147600</v>
+        <v>147200</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2706,10 +2706,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>416000</v>
+        <v>414900</v>
       </c>
       <c r="E83" s="3">
-        <v>431500</v>
+        <v>430300</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2886,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1408900</v>
+        <v>1405000</v>
       </c>
       <c r="E89" s="3">
-        <v>955200</v>
+        <v>952600</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2930,10 +2930,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-926600</v>
+        <v>-924100</v>
       </c>
       <c r="E91" s="3">
-        <v>-711600</v>
+        <v>-709600</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -3020,10 +3020,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>213800</v>
+        <v>213200</v>
       </c>
       <c r="E94" s="3">
-        <v>-418000</v>
+        <v>-416800</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3064,10 +3064,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-632300</v>
+        <v>-630600</v>
       </c>
       <c r="E96" s="3">
-        <v>-664600</v>
+        <v>-662800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1895100</v>
+        <v>-1889900</v>
       </c>
       <c r="E100" s="3">
-        <v>-733500</v>
+        <v>-731500</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3214,10 +3214,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-333900</v>
+        <v>-333000</v>
       </c>
       <c r="E101" s="3">
-        <v>-222400</v>
+        <v>-221800</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3244,10 +3244,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-606300</v>
+        <v>-604700</v>
       </c>
       <c r="E102" s="3">
-        <v>-418700</v>
+        <v>-417600</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
@@ -713,13 +713,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>12172100</v>
+        <v>12192100</v>
       </c>
       <c r="E8" s="3">
-        <v>8720300</v>
+        <v>8734600</v>
       </c>
       <c r="F8" s="3">
-        <v>8722900</v>
+        <v>8737300</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -743,13 +743,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9430000</v>
+        <v>9445500</v>
       </c>
       <c r="E9" s="3">
-        <v>6387800</v>
+        <v>6398300</v>
       </c>
       <c r="F9" s="3">
-        <v>6274600</v>
+        <v>6285000</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -773,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2742100</v>
+        <v>2746600</v>
       </c>
       <c r="E10" s="3">
-        <v>2332500</v>
+        <v>2336400</v>
       </c>
       <c r="F10" s="3">
-        <v>2448300</v>
+        <v>2452300</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -880,10 +880,10 @@
         <v>19600</v>
       </c>
       <c r="E14" s="3">
-        <v>36300</v>
+        <v>36400</v>
       </c>
       <c r="F14" s="3">
-        <v>126500</v>
+        <v>126700</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10751700</v>
+        <v>10769300</v>
       </c>
       <c r="E17" s="3">
-        <v>7680600</v>
+        <v>7693200</v>
       </c>
       <c r="F17" s="3">
-        <v>7642600</v>
+        <v>7655200</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -978,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1420500</v>
+        <v>1422800</v>
       </c>
       <c r="E18" s="3">
-        <v>1039700</v>
+        <v>1041400</v>
       </c>
       <c r="F18" s="3">
-        <v>1080300</v>
+        <v>1082100</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1022,13 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>559300</v>
+        <v>560300</v>
       </c>
       <c r="E20" s="3">
-        <v>471800</v>
+        <v>472600</v>
       </c>
       <c r="F20" s="3">
-        <v>636200</v>
+        <v>637300</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1052,10 +1052,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2394600</v>
+        <v>2398500</v>
       </c>
       <c r="E21" s="3">
-        <v>1941800</v>
+        <v>1945000</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1082,13 +1082,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>689100</v>
+        <v>690200</v>
       </c>
       <c r="E22" s="3">
-        <v>333600</v>
+        <v>334100</v>
       </c>
       <c r="F22" s="3">
-        <v>395600</v>
+        <v>396300</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1112,13 +1112,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1290700</v>
+        <v>1292800</v>
       </c>
       <c r="E23" s="3">
-        <v>1178000</v>
+        <v>1179900</v>
       </c>
       <c r="F23" s="3">
-        <v>1320900</v>
+        <v>1323100</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1142,13 +1142,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>769000</v>
+        <v>770300</v>
       </c>
       <c r="E24" s="3">
-        <v>628000</v>
+        <v>629100</v>
       </c>
       <c r="F24" s="3">
-        <v>723800</v>
+        <v>725000</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1202,13 +1202,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>521700</v>
+        <v>522600</v>
       </c>
       <c r="E26" s="3">
-        <v>549900</v>
+        <v>550800</v>
       </c>
       <c r="F26" s="3">
-        <v>597100</v>
+        <v>598100</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1232,13 +1232,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>124800</v>
+        <v>125000</v>
       </c>
       <c r="E27" s="3">
-        <v>159700</v>
+        <v>160000</v>
       </c>
       <c r="F27" s="3">
-        <v>147200</v>
+        <v>147400</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1382,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-559300</v>
+        <v>-560300</v>
       </c>
       <c r="E32" s="3">
-        <v>-471800</v>
+        <v>-472600</v>
       </c>
       <c r="F32" s="3">
-        <v>-636200</v>
+        <v>-637300</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1412,13 +1412,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>124800</v>
+        <v>125000</v>
       </c>
       <c r="E33" s="3">
-        <v>159700</v>
+        <v>160000</v>
       </c>
       <c r="F33" s="3">
-        <v>147200</v>
+        <v>147400</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1472,13 +1472,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>124800</v>
+        <v>125000</v>
       </c>
       <c r="E35" s="3">
-        <v>159700</v>
+        <v>160000</v>
       </c>
       <c r="F35" s="3">
-        <v>147200</v>
+        <v>147400</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1565,10 +1565,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6809300</v>
+        <v>6820400</v>
       </c>
       <c r="E41" s="3">
-        <v>7378400</v>
+        <v>7390500</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1595,10 +1595,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1979900</v>
+        <v>1983200</v>
       </c>
       <c r="E42" s="3">
-        <v>1832400</v>
+        <v>1835400</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1625,10 +1625,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4571900</v>
+        <v>4579400</v>
       </c>
       <c r="E43" s="3">
-        <v>2533000</v>
+        <v>2537100</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1655,10 +1655,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10093700</v>
+        <v>10110300</v>
       </c>
       <c r="E44" s="3">
-        <v>10782200</v>
+        <v>10800000</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1685,10 +1685,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1622500</v>
+        <v>1625200</v>
       </c>
       <c r="E45" s="3">
-        <v>2168600</v>
+        <v>2172200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1715,10 +1715,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21975400</v>
+        <v>22011500</v>
       </c>
       <c r="E46" s="3">
-        <v>24694600</v>
+        <v>24735100</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1745,10 +1745,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18905400</v>
+        <v>18936400</v>
       </c>
       <c r="E47" s="3">
-        <v>17483700</v>
+        <v>17512400</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1775,10 +1775,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34130000</v>
+        <v>34186100</v>
       </c>
       <c r="E48" s="3">
-        <v>33304100</v>
+        <v>33358800</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1805,10 +1805,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5525700</v>
+        <v>5534800</v>
       </c>
       <c r="E49" s="3">
-        <v>2736600</v>
+        <v>2741100</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1895,10 +1895,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7398500</v>
+        <v>7410600</v>
       </c>
       <c r="E52" s="3">
-        <v>3072400</v>
+        <v>3077500</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1955,10 +1955,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>77856300</v>
+        <v>77984200</v>
       </c>
       <c r="E54" s="3">
-        <v>81291400</v>
+        <v>81424900</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2013,10 +2013,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11639200</v>
+        <v>11658300</v>
       </c>
       <c r="E57" s="3">
-        <v>4407500</v>
+        <v>4414700</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2043,10 +2043,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6818900</v>
+        <v>6830100</v>
       </c>
       <c r="E58" s="3">
-        <v>6590800</v>
+        <v>6601600</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2073,10 +2073,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17697300</v>
+        <v>17726400</v>
       </c>
       <c r="E59" s="3">
-        <v>11094200</v>
+        <v>11112400</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2103,10 +2103,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22625700</v>
+        <v>22662800</v>
       </c>
       <c r="E60" s="3">
-        <v>22092400</v>
+        <v>22128700</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2133,10 +2133,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18183500</v>
+        <v>18213400</v>
       </c>
       <c r="E61" s="3">
-        <v>18863600</v>
+        <v>18894600</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2163,10 +2163,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4058800</v>
+        <v>4065500</v>
       </c>
       <c r="E62" s="3">
-        <v>3504900</v>
+        <v>3510600</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2283,10 +2283,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46292500</v>
+        <v>46368500</v>
       </c>
       <c r="E66" s="3">
-        <v>47928400</v>
+        <v>48007200</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2447,10 +2447,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>30521800</v>
+        <v>15504300</v>
       </c>
       <c r="E72" s="3">
-        <v>17255600</v>
+        <v>17283900</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2567,10 +2567,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31563900</v>
+        <v>31615700</v>
       </c>
       <c r="E76" s="3">
-        <v>33363000</v>
+        <v>33417800</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2662,13 +2662,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>124800</v>
+        <v>125000</v>
       </c>
       <c r="E81" s="3">
-        <v>159700</v>
+        <v>160000</v>
       </c>
       <c r="F81" s="3">
-        <v>147200</v>
+        <v>147400</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2706,10 +2706,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>414900</v>
+        <v>415500</v>
       </c>
       <c r="E83" s="3">
-        <v>430300</v>
+        <v>431100</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2886,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1405000</v>
+        <v>1407300</v>
       </c>
       <c r="E89" s="3">
-        <v>952600</v>
+        <v>954200</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2930,10 +2930,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-924100</v>
+        <v>-925600</v>
       </c>
       <c r="E91" s="3">
-        <v>-709600</v>
+        <v>-710800</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -3020,10 +3020,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>213200</v>
+        <v>213600</v>
       </c>
       <c r="E94" s="3">
-        <v>-416800</v>
+        <v>-417500</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3064,10 +3064,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-630600</v>
+        <v>-631600</v>
       </c>
       <c r="E96" s="3">
-        <v>-662800</v>
+        <v>-663800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1889900</v>
+        <v>-1893000</v>
       </c>
       <c r="E100" s="3">
-        <v>-731500</v>
+        <v>-732700</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3214,10 +3214,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-333000</v>
+        <v>-333600</v>
       </c>
       <c r="E101" s="3">
-        <v>-221800</v>
+        <v>-222200</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3244,10 +3244,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-604700</v>
+        <v>-605700</v>
       </c>
       <c r="E102" s="3">
-        <v>-417600</v>
+        <v>-418300</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NDVLY_YR_FIN.xlsx
@@ -713,13 +713,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>12192100</v>
+        <v>12209300</v>
       </c>
       <c r="E8" s="3">
-        <v>8734600</v>
+        <v>8746900</v>
       </c>
       <c r="F8" s="3">
-        <v>8737300</v>
+        <v>8749500</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -743,13 +743,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9445500</v>
+        <v>9458800</v>
       </c>
       <c r="E9" s="3">
-        <v>6398300</v>
+        <v>6407300</v>
       </c>
       <c r="F9" s="3">
-        <v>6285000</v>
+        <v>6293800</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -773,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2746600</v>
+        <v>2750500</v>
       </c>
       <c r="E10" s="3">
-        <v>2336400</v>
+        <v>2339600</v>
       </c>
       <c r="F10" s="3">
-        <v>2452300</v>
+        <v>2455800</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -883,7 +883,7 @@
         <v>36400</v>
       </c>
       <c r="F14" s="3">
-        <v>126700</v>
+        <v>126900</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10769300</v>
+        <v>10784500</v>
       </c>
       <c r="E17" s="3">
-        <v>7693200</v>
+        <v>7704000</v>
       </c>
       <c r="F17" s="3">
-        <v>7655200</v>
+        <v>7665900</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -978,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1422800</v>
+        <v>1424800</v>
       </c>
       <c r="E18" s="3">
-        <v>1041400</v>
+        <v>1042900</v>
       </c>
       <c r="F18" s="3">
-        <v>1082100</v>
+        <v>1083600</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1022,13 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>560300</v>
+        <v>561000</v>
       </c>
       <c r="E20" s="3">
-        <v>472600</v>
+        <v>473300</v>
       </c>
       <c r="F20" s="3">
-        <v>637300</v>
+        <v>638200</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1052,10 +1052,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2398500</v>
+        <v>2401700</v>
       </c>
       <c r="E21" s="3">
-        <v>1945000</v>
+        <v>1947600</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1082,13 +1082,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>690200</v>
+        <v>691200</v>
       </c>
       <c r="E22" s="3">
-        <v>334100</v>
+        <v>334600</v>
       </c>
       <c r="F22" s="3">
-        <v>396300</v>
+        <v>396800</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1112,13 +1112,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1292800</v>
+        <v>1294600</v>
       </c>
       <c r="E23" s="3">
-        <v>1179900</v>
+        <v>1181600</v>
       </c>
       <c r="F23" s="3">
-        <v>1323100</v>
+        <v>1324900</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1142,13 +1142,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>770300</v>
+        <v>771400</v>
       </c>
       <c r="E24" s="3">
-        <v>629100</v>
+        <v>630000</v>
       </c>
       <c r="F24" s="3">
-        <v>725000</v>
+        <v>726000</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1202,13 +1202,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>522600</v>
+        <v>523300</v>
       </c>
       <c r="E26" s="3">
-        <v>550800</v>
+        <v>551600</v>
       </c>
       <c r="F26" s="3">
-        <v>598100</v>
+        <v>598900</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1232,13 +1232,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>125000</v>
+        <v>125200</v>
       </c>
       <c r="E27" s="3">
-        <v>160000</v>
+        <v>160200</v>
       </c>
       <c r="F27" s="3">
-        <v>147400</v>
+        <v>147700</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1382,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-560300</v>
+        <v>-561000</v>
       </c>
       <c r="E32" s="3">
-        <v>-472600</v>
+        <v>-473300</v>
       </c>
       <c r="F32" s="3">
-        <v>-637300</v>
+        <v>-638200</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1412,13 +1412,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>125000</v>
+        <v>125200</v>
       </c>
       <c r="E33" s="3">
-        <v>160000</v>
+        <v>160200</v>
       </c>
       <c r="F33" s="3">
-        <v>147400</v>
+        <v>147700</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1472,13 +1472,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>125000</v>
+        <v>125200</v>
       </c>
       <c r="E35" s="3">
-        <v>160000</v>
+        <v>160200</v>
       </c>
       <c r="F35" s="3">
-        <v>147400</v>
+        <v>147700</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1565,10 +1565,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6820400</v>
+        <v>6830000</v>
       </c>
       <c r="E41" s="3">
-        <v>7390500</v>
+        <v>7400900</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1595,10 +1595,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1983200</v>
+        <v>1986000</v>
       </c>
       <c r="E42" s="3">
-        <v>1835400</v>
+        <v>1838000</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1625,10 +1625,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4579400</v>
+        <v>4585900</v>
       </c>
       <c r="E43" s="3">
-        <v>2537100</v>
+        <v>2540700</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1655,10 +1655,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10110300</v>
+        <v>10124500</v>
       </c>
       <c r="E44" s="3">
-        <v>10800000</v>
+        <v>10815100</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1685,10 +1685,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1625200</v>
+        <v>1627500</v>
       </c>
       <c r="E45" s="3">
-        <v>2172200</v>
+        <v>2175200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1715,10 +1715,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22011500</v>
+        <v>22042400</v>
       </c>
       <c r="E46" s="3">
-        <v>24735100</v>
+        <v>24769900</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1745,10 +1745,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18936400</v>
+        <v>18963000</v>
       </c>
       <c r="E47" s="3">
-        <v>17512400</v>
+        <v>17537000</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1775,10 +1775,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34186100</v>
+        <v>34234100</v>
       </c>
       <c r="E48" s="3">
-        <v>33358800</v>
+        <v>33405700</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1805,10 +1805,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5534800</v>
+        <v>5542500</v>
       </c>
       <c r="E49" s="3">
-        <v>2741100</v>
+        <v>2745000</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1895,10 +1895,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7410600</v>
+        <v>7421000</v>
       </c>
       <c r="E52" s="3">
-        <v>3077500</v>
+        <v>3081800</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1955,10 +1955,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>77984200</v>
+        <v>78093900</v>
       </c>
       <c r="E54" s="3">
-        <v>81424900</v>
+        <v>81539400</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2013,10 +2013,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11658300</v>
+        <v>11674700</v>
       </c>
       <c r="E57" s="3">
-        <v>4414700</v>
+        <v>4420900</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2043,10 +2043,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6830100</v>
+        <v>6839700</v>
       </c>
       <c r="E58" s="3">
-        <v>6601600</v>
+        <v>6610900</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2073,10 +2073,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17726400</v>
+        <v>17751300</v>
       </c>
       <c r="E59" s="3">
-        <v>11112400</v>
+        <v>11128000</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2103,10 +2103,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22662800</v>
+        <v>22694700</v>
       </c>
       <c r="E60" s="3">
-        <v>22128700</v>
+        <v>22159800</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2133,10 +2133,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18213400</v>
+        <v>18239000</v>
       </c>
       <c r="E61" s="3">
-        <v>18894600</v>
+        <v>18921100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2163,10 +2163,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4065500</v>
+        <v>4071200</v>
       </c>
       <c r="E62" s="3">
-        <v>3510600</v>
+        <v>3515600</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2283,10 +2283,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46368500</v>
+        <v>46433700</v>
       </c>
       <c r="E66" s="3">
-        <v>48007200</v>
+        <v>48074700</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2447,10 +2447,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15504300</v>
+        <v>15526100</v>
       </c>
       <c r="E72" s="3">
-        <v>17283900</v>
+        <v>17308200</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2567,10 +2567,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31615700</v>
+        <v>31660200</v>
       </c>
       <c r="E76" s="3">
-        <v>33417800</v>
+        <v>33464700</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2662,13 +2662,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>125000</v>
+        <v>125200</v>
       </c>
       <c r="E81" s="3">
-        <v>160000</v>
+        <v>160200</v>
       </c>
       <c r="F81" s="3">
-        <v>147400</v>
+        <v>147700</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2706,10 +2706,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>415500</v>
+        <v>416100</v>
       </c>
       <c r="E83" s="3">
-        <v>431100</v>
+        <v>431700</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2886,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1407300</v>
+        <v>1409300</v>
       </c>
       <c r="E89" s="3">
-        <v>954200</v>
+        <v>955500</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2930,10 +2930,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-925600</v>
+        <v>-926900</v>
       </c>
       <c r="E91" s="3">
-        <v>-710800</v>
+        <v>-711800</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -3020,10 +3020,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>213600</v>
+        <v>213900</v>
       </c>
       <c r="E94" s="3">
-        <v>-417500</v>
+        <v>-418100</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3064,10 +3064,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-631600</v>
+        <v>-632500</v>
       </c>
       <c r="E96" s="3">
-        <v>-663800</v>
+        <v>-664800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1893000</v>
+        <v>-1895700</v>
       </c>
       <c r="E100" s="3">
-        <v>-732700</v>
+        <v>-733700</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3214,10 +3214,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-333600</v>
+        <v>-334000</v>
       </c>
       <c r="E101" s="3">
-        <v>-222200</v>
+        <v>-222500</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3244,10 +3244,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-605700</v>
+        <v>-606500</v>
       </c>
       <c r="E102" s="3">
-        <v>-418300</v>
+        <v>-418900</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>
